--- a/docs/sample-data/Tech-Conference-Tasks.xlsx
+++ b/docs/sample-data/Tech-Conference-Tasks.xlsx
@@ -459,10 +459,10 @@
         <v>Planning</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-01-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-01-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E2" t="str">
         <v>Completed</v>
@@ -497,10 +497,10 @@
         <v>Planning</v>
       </c>
       <c r="C3" t="str">
-        <v>2025-01-07</v>
+        <v>2026-05-08</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-01-17</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E3" t="str">
         <v>Completed</v>
@@ -535,10 +535,10 @@
         <v>Planning</v>
       </c>
       <c r="C4" t="str">
-        <v>2025-01-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-01-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E4" t="str">
         <v>Completed</v>
@@ -573,10 +573,10 @@
         <v>Planning</v>
       </c>
       <c r="C5" t="str">
-        <v>2025-01-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-02-07</v>
+        <v>2026-06-08</v>
       </c>
       <c r="E5" t="str">
         <v>Completed</v>
@@ -597,7 +597,7 @@
         <v>Finalize venue selection and execute contract.</v>
       </c>
       <c r="K5" t="str">
-        <v>Grand Convention Center booked for Jun 2–3. Deposit paid.</v>
+        <v>Grand Convention Center booked for Oct 1–2. Deposit paid.</v>
       </c>
       <c r="L5" t="str">
         <v>Yes</v>
@@ -611,10 +611,10 @@
         <v>Planning</v>
       </c>
       <c r="C6" t="str">
-        <v>2025-02-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="E6" t="str">
         <v>Completed</v>
@@ -649,10 +649,10 @@
         <v>Content</v>
       </c>
       <c r="C7" t="str">
-        <v>2025-02-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-03-07</v>
+        <v>2026-07-06</v>
       </c>
       <c r="E7" t="str">
         <v>Completed</v>
@@ -687,10 +687,10 @@
         <v>Content</v>
       </c>
       <c r="C8" t="str">
-        <v>2025-02-24</v>
+        <v>2026-06-25</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-03-28</v>
+        <v>2026-07-20</v>
       </c>
       <c r="E8" t="str">
         <v>Completed</v>
@@ -725,10 +725,10 @@
         <v>Content</v>
       </c>
       <c r="C9" t="str">
-        <v>2025-03-31</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-04-11</v>
+        <v>2026-08-10</v>
       </c>
       <c r="E9" t="str">
         <v>Completed</v>
@@ -763,10 +763,10 @@
         <v>Content</v>
       </c>
       <c r="C10" t="str">
-        <v>2025-04-28</v>
+        <v>2026-08-27</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-05-09</v>
+        <v>2026-09-07</v>
       </c>
       <c r="E10" t="str">
         <v>In Progress</v>
@@ -787,7 +787,7 @@
         <v>Design attendee satisfaction survey targeting NPS &gt; 60.</v>
       </c>
       <c r="K10" t="str">
-        <v>Draft in SurveyMonkey. Review with Sarah by May 7.</v>
+        <v>Draft in SurveyMonkey. Review with Sarah by Sep 4.</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -801,10 +801,10 @@
         <v>Logistics</v>
       </c>
       <c r="C11" t="str">
-        <v>2025-02-17</v>
+        <v>2026-06-18</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-03-14</v>
+        <v>2026-07-13</v>
       </c>
       <c r="E11" t="str">
         <v>Completed</v>
@@ -839,10 +839,10 @@
         <v>Logistics</v>
       </c>
       <c r="C12" t="str">
-        <v>2025-02-24</v>
+        <v>2026-06-25</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-03-21</v>
+        <v>2026-07-20</v>
       </c>
       <c r="E12" t="str">
         <v>Completed</v>
@@ -877,10 +877,10 @@
         <v>Logistics</v>
       </c>
       <c r="C13" t="str">
-        <v>2025-04-07</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-05-02</v>
+        <v>2026-08-31</v>
       </c>
       <c r="E13" t="str">
         <v>In Progress</v>
@@ -915,10 +915,10 @@
         <v>Logistics</v>
       </c>
       <c r="C14" t="str">
-        <v>2025-04-14</v>
+        <v>2026-08-13</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-05-09</v>
+        <v>2026-09-07</v>
       </c>
       <c r="E14" t="str">
         <v>In Progress</v>
@@ -939,7 +939,7 @@
         <v>Design and print name badges; procure branded tote bags and lanyards.</v>
       </c>
       <c r="K14" t="str">
-        <v>Badge design approved. Print order placed — delivery May 5.</v>
+        <v>Badge design approved. Print order placed — delivery Sep 3.</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Logistics</v>
       </c>
       <c r="C15" t="str">
-        <v>2025-04-21</v>
+        <v>2026-08-20</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-05-16</v>
+        <v>2026-09-14</v>
       </c>
       <c r="E15" t="str">
         <v>In Progress</v>
@@ -977,7 +977,7 @@
         <v>Recruit 30 event-day volunteers and run a 2-hour orientation session.</v>
       </c>
       <c r="K15" t="str">
-        <v>22 volunteers confirmed. Orientation scheduled for May 14.</v>
+        <v>22 volunteers confirmed. Orientation scheduled for Sep 11.</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -991,10 +991,10 @@
         <v>Logistics</v>
       </c>
       <c r="C16" t="str">
-        <v>2025-05-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-05-30</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E16" t="str">
         <v>Not Started</v>
@@ -1029,10 +1029,10 @@
         <v>Logistics</v>
       </c>
       <c r="C17" t="str">
-        <v>2025-06-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-06-02</v>
+        <v>2026-10-01</v>
       </c>
       <c r="E17" t="str">
         <v>Not Started</v>
@@ -1067,10 +1067,10 @@
         <v>Logistics</v>
       </c>
       <c r="C18" t="str">
-        <v>2025-06-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-06-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="E18" t="str">
         <v>Not Started</v>
@@ -1105,10 +1105,10 @@
         <v>Logistics</v>
       </c>
       <c r="C19" t="str">
-        <v>2025-06-09</v>
+        <v>2026-10-08</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-06-13</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E19" t="str">
         <v>Not Started</v>
@@ -1129,7 +1129,7 @@
         <v>Review venue performance with event manager; document lessons learned.</v>
       </c>
       <c r="K19" t="str">
-        <v>Required for 2026 venue renewal negotiation.</v>
+        <v>Required for 2027 venue renewal negotiation.</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1143,10 +1143,10 @@
         <v>Marketing</v>
       </c>
       <c r="C20" t="str">
-        <v>2025-03-10</v>
+        <v>2026-07-09</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-03-28</v>
+        <v>2026-07-27</v>
       </c>
       <c r="E20" t="str">
         <v>Completed</v>
@@ -1181,10 +1181,10 @@
         <v>Marketing</v>
       </c>
       <c r="C21" t="str">
-        <v>2025-03-17</v>
+        <v>2026-07-16</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-04-04</v>
+        <v>2026-08-03</v>
       </c>
       <c r="E21" t="str">
         <v>Completed</v>
@@ -1205,7 +1205,7 @@
         <v>Launch public conference website with agenda, speakers, and sponsor info.</v>
       </c>
       <c r="K21" t="str">
-        <v>Live at techconf2025.contoso.com. 4,200 unique visitors in week 1.</v>
+        <v>Live at techconf2026.contoso.com. 4,200 unique visitors in week 1.</v>
       </c>
       <c r="L21" t="str">
         <v>Yes</v>
@@ -1219,10 +1219,10 @@
         <v>Marketing</v>
       </c>
       <c r="C22" t="str">
-        <v>2025-03-24</v>
+        <v>2026-07-23</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-04-18</v>
+        <v>2026-08-17</v>
       </c>
       <c r="E22" t="str">
         <v>Completed</v>
@@ -1257,10 +1257,10 @@
         <v>Marketing</v>
       </c>
       <c r="C23" t="str">
-        <v>2025-03-03</v>
+        <v>2026-07-02</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-04-25</v>
+        <v>2026-08-24</v>
       </c>
       <c r="E23" t="str">
         <v>In Progress</v>
@@ -1281,7 +1281,7 @@
         <v>Close Gold, Silver, and Bronze sponsorship packages.</v>
       </c>
       <c r="K23" t="str">
-        <v>4 of 6 slots filled. 2 negotiations active — close expected by Apr 18.</v>
+        <v>4 of 6 slots filled. 2 negotiations active — close expected by Aug 17.</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1295,10 +1295,10 @@
         <v>Marketing</v>
       </c>
       <c r="C24" t="str">
-        <v>2025-05-05</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-06-01</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E24" t="str">
         <v>Not Started</v>
@@ -1333,10 +1333,10 @@
         <v>Marketing</v>
       </c>
       <c r="C25" t="str">
-        <v>2025-05-19</v>
+        <v>2026-09-17</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-05-23</v>
+        <v>2026-09-21</v>
       </c>
       <c r="E25" t="str">
         <v>Not Started</v>
@@ -1357,7 +1357,7 @@
         <v>Send final logistics email to registered attendees with schedule and parking.</v>
       </c>
       <c r="K25" t="str">
-        <v>Registration closes May 16. Use Mailchimp template #Conference-Final.</v>
+        <v>Registration closes Sep 14. Use Mailchimp template #Conference-Final.</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1365,16 +1365,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sponsor Debrief &amp; 2026 Renewals</v>
+        <v>Sponsor Debrief &amp; 2027 Renewals</v>
       </c>
       <c r="B26" t="str">
         <v>Marketing</v>
       </c>
       <c r="C26" t="str">
-        <v>2025-06-04</v>
+        <v>2026-10-03</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-06-20</v>
+        <v>2026-10-19</v>
       </c>
       <c r="E26" t="str">
         <v>Not Started</v>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="str">
-        <v>Present ROI metrics to all sponsors; pitch 2026 renewal packages.</v>
+        <v>Present ROI metrics to all sponsors; pitch 2027 renewal packages.</v>
       </c>
       <c r="K26" t="str">
-        <v>Pre-meeting decks due June 9. Target 80% renewal rate.</v>
+        <v>Pre-meeting decks due Oct 5. Target 80% renewal rate.</v>
       </c>
       <c r="L26" t="str">
         <v/>
